--- a/Table/Excel/Text_Dialogue.xlsx
+++ b/Table/Excel/Text_Dialogue.xlsx
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Dialogue" displayName="Text_Dialogue" ref="B2:E50" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Dialogue" displayName="Text_Dialogue" ref="B2:E51" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E51"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E50"/>
+  <dimension ref="B2:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="4" min="1" max="1"/>
@@ -1023,7 +1023,7 @@
       <c r="E33" s="1" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="0" t="n">
         <v>32</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1039,7 +1039,7 @@
       <c r="E34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="0" t="n">
         <v>33</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       <c r="E35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>34</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       <c r="E36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="0" t="n">
         <v>35</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       <c r="E37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>36</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       <c r="E38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>37</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="E39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" t="n">
+      <c r="B40" s="0" t="n">
         <v>38</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       <c r="E40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>39</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       <c r="E41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>40</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="E42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" t="n">
+      <c r="B43" s="0" t="n">
         <v>41</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="E43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" t="n">
+      <c r="B44" s="0" t="n">
         <v>42</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="E44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" t="n">
+      <c r="B45" s="0" t="n">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       <c r="E45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" t="n">
+      <c r="B46" s="0" t="n">
         <v>44</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1231,7 +1231,7 @@
       <c r="E46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" t="n">
+      <c r="B47" s="0" t="n">
         <v>45</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1247,7 +1247,7 @@
       <c r="E47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" t="n">
+      <c r="B48" s="0" t="n">
         <v>46</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1263,7 +1263,7 @@
       <c r="E48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" t="n">
+      <c r="B49" s="0" t="n">
         <v>47</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="E49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" t="n">
+      <c r="B50" s="0" t="n">
         <v>48</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1293,6 +1293,26 @@
         </is>
       </c>
       <c r="E50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1130</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>부탁? 그럼 광장 사람들이랑 얼굴부터 트고 와! 다들 탐정 양반을 궁금해하거든.</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>A favor? Then go say hi to folks in the plaza first! Everyone's curious about you.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Table/Excel/Text_Dialogue.xlsx
+++ b/Table/Excel/Text_Dialogue.xlsx
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Dialogue" displayName="Text_Dialogue" ref="B2:E51" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Dialogue" displayName="Text_Dialogue" ref="B2:E57" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E57"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E51"/>
+  <dimension ref="B2:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="4" min="1" max="1"/>
@@ -1295,7 +1295,7 @@
       <c r="E50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" t="n">
+      <c r="B51" s="0" t="n">
         <v>49</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -1311,6 +1311,126 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>A favor? Then go say hi to folks in the plaza first! Everyone's curious about you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1700</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1710</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1730</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1800</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1810</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>dialogue.1830</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>테스트 문구</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Test line</t>
         </is>
       </c>
     </row>
